--- a/examples/MNL_modeChoice_RP_WTP.xlsx
+++ b/examples/MNL_modeChoice_RP_WTP.xlsx
@@ -13,8 +13,7 @@
     <workbookView xWindow="380" yWindow="460" windowWidth="28040" windowHeight="17040" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Expressions" r:id="rId4" sheetId="2"/>
+    <sheet name="Expressions" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -413,15 +412,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -459,22 +449,22 @@
         <v>0.6093287523842155</v>
       </c>
       <c r="C2">
-        <v>0.188743893497415</v>
+        <v>0.18874389349741216</v>
       </c>
       <c r="D2">
-        <v>3.2283362449157105</v>
+        <v>3.228336244915759</v>
       </c>
       <c r="E2">
-        <v>0.0012451252414449332</v>
+        <v>0.0012451252414447112</v>
       </c>
       <c r="F2">
-        <v>0.18794420729072164</v>
+        <v>0.18794420729071754</v>
       </c>
       <c r="G2">
-        <v>3.242072534013644</v>
+        <v>3.242072534013715</v>
       </c>
       <c r="H2">
-        <v>0.001186638165906917</v>
+        <v>0.0011866381659064729</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -482,25 +472,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0.26058639294994473</v>
+        <v>0.26058639294994557</v>
       </c>
       <c r="C3">
-        <v>0.07780445605623416</v>
+        <v>0.07780445605623351</v>
       </c>
       <c r="D3">
-        <v>3.3492476672750287</v>
+        <v>3.3492476672750673</v>
       </c>
       <c r="E3">
-        <v>0.0008103132736099194</v>
+        <v>0.0008103132736096974</v>
       </c>
       <c r="F3">
-        <v>0.07650354268588136</v>
+        <v>0.07650354268588301</v>
       </c>
       <c r="G3">
-        <v>3.4062003379359274</v>
+        <v>3.4062003379358647</v>
       </c>
       <c r="H3">
-        <v>0.0006587382150238241</v>
+        <v>0.0006587382150240462</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -508,25 +498,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>0.10740443300447541</v>
+        <v>0.10740443300447526</v>
       </c>
       <c r="C4">
-        <v>0.04506437715133166</v>
+        <v>0.04506437715133213</v>
       </c>
       <c r="D4">
-        <v>2.3833555414246215</v>
+        <v>2.3833555414245935</v>
       </c>
       <c r="E4">
-        <v>0.017155616234818538</v>
+        <v>0.01715561623481987</v>
       </c>
       <c r="F4">
-        <v>0.04520626767764224</v>
+        <v>0.04520626767764363</v>
       </c>
       <c r="G4">
-        <v>2.375874818296372</v>
+        <v>2.3758748182962957</v>
       </c>
       <c r="H4">
-        <v>0.01750740118720162</v>
+        <v>0.017507401187205396</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -534,25 +524,25 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.3310836306986038</v>
+        <v>0.33108363069860286</v>
       </c>
       <c r="C5">
-        <v>0.12797716669505205</v>
+        <v>0.12797716669505255</v>
       </c>
       <c r="D5">
-        <v>2.5870523566717187</v>
+        <v>2.5870523566717014</v>
       </c>
       <c r="E5">
-        <v>0.009680088226916572</v>
+        <v>0.009680088226917016</v>
       </c>
       <c r="F5">
-        <v>0.12798848588780876</v>
+        <v>0.1279884858878155</v>
       </c>
       <c r="G5">
-        <v>2.58682355996322</v>
+        <v>2.5868235599630762</v>
       </c>
       <c r="H5">
-        <v>0.00968651786681396</v>
+        <v>0.009686517866817956</v>
       </c>
     </row>
   </sheetData>
